--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45028-2023 artfynd.xlsx
+++ b/artfynd/A 45028-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722421</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136722422</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
